--- a/data/trans_orig/P56S_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P56S_R-Edad-trans_orig.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12014</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>19426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30537</t>
+          <t>30587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26706</t>
+          <t>26416</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>33754</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42224</t>
+          <t>42921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57943</t>
+          <t>57996</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72055</t>
+          <t>72243</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>90402</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>18109</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>21181</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45004</t>
+          <t>44884</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>75649</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>97234</t>
+          <t>97613</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>117320</t>
+          <t>117862</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21243</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>22073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34371</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>39887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52658</t>
+          <t>53263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>14618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23438</t>
+          <t>22429</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>26898</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29422</t>
+          <t>29460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34336</t>
+          <t>34869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32669</t>
+          <t>33480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40270</t>
+          <t>39469</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34529</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48324</t>
+          <t>47550</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80775</t>
+          <t>80091</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106098</t>
+          <t>106692</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120455</t>
+          <t>120474</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149414</t>
+          <t>151182</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>13421</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>13506</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25428</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6344,12 +6344,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>28277</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>10399</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34035</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17386</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>39219</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6633,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>32640</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6683,47 +6683,47 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>29485</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>20127</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>42173</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
           <t>7,09%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>29485</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>19627</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>39920</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>10,39%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50636</t>
+          <t>51029</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>67495</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106411</t>
+          <t>107206</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>136257</t>
+          <t>136303</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>165477</t>
+          <t>165049</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>197382</t>
+          <t>198337</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24381</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36015</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51421</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -8566,12 +8566,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>817</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -8792,12 +8792,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>15758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35008</t>
+          <t>35038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23174</t>
+          <t>22562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44824</t>
+          <t>47104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>14082</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24191</t>
+          <t>24414</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36714</t>
+          <t>37196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63697</t>
+          <t>63961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88140</t>
+          <t>89288</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9068,12 +9068,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93348</t>
+          <t>92258</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121988</t>
+          <t>122015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9103,12 +9103,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -9131,12 +9131,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9146,12 +9146,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30411</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -9587,12 +9587,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21278</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>37253</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48625</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -9926,12 +9926,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>41406</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56725</t>
+          <t>55912</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10054,12 +10054,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86700</t>
+          <t>86382</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>116375</t>
+          <t>116254</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>136363</t>
+          <t>135233</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>168629</t>
+          <t>167702</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,76%</t>
         </is>
       </c>
     </row>
@@ -10152,12 +10152,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>41034</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>23786</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>47572</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -10652,12 +10652,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -10687,12 +10687,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -10720,32 +10720,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10755,32 +10755,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10790,32 +10790,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -10833,32 +10833,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10868,17 +10868,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10903,32 +10903,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>497</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>387</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11104,12 +11104,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>884</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -11182,12 +11182,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -11197,7 +11197,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11207,32 +11207,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>453</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11242,32 +11242,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -11285,32 +11285,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>23679</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11320,32 +11320,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36881</t>
+          <t>40952</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>35741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41496</t>
+          <t>45871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11355,32 +11355,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59454</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53387</t>
+          <t>57732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64879</t>
+          <t>70776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -11398,32 +11398,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11433,32 +11433,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11468,32 +11468,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -11511,17 +11511,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29651</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29651</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29651</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11546,17 +11546,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52997</t>
+          <t>59462</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52997</t>
+          <t>59462</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52997</t>
+          <t>59462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11581,17 +11581,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>82648</t>
+          <t>90444</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>82648</t>
+          <t>90444</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82648</t>
+          <t>90444</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11628,32 +11628,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11663,32 +11663,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11698,32 +11698,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -11741,32 +11741,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11776,32 +11776,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19242</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11811,32 +11811,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>27095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -11854,32 +11854,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>18796</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11889,32 +11889,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41174</t>
+          <t>44599</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>35716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50593</t>
+          <t>53404</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11924,32 +11924,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>53631</t>
+          <t>57342</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>44722</t>
+          <t>47357</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>63114</t>
+          <t>68891</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -11967,32 +11967,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12002,32 +12002,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12037,32 +12037,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -12080,32 +12080,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12115,32 +12115,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12150,32 +12150,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>15447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>29955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -12193,32 +12193,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12228,32 +12228,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>19035</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12263,32 +12263,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>16232</t>
+          <t>17838</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>11791</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -12306,32 +12306,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>42687</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>35528</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45752</t>
+          <t>49883</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12341,32 +12341,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>95741</t>
+          <t>104903</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85444</t>
+          <t>93995</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>105491</t>
+          <t>115830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12376,32 +12376,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>135034</t>
+          <t>147590</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>122592</t>
+          <t>134843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147398</t>
+          <t>161760</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -12419,32 +12419,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12454,32 +12454,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12489,32 +12489,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -12532,17 +12532,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72408</t>
+          <t>77594</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72408</t>
+          <t>77594</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72408</t>
+          <t>77594</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12567,17 +12567,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>198036</t>
+          <t>215967</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>198036</t>
+          <t>215967</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>198036</t>
+          <t>215967</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12602,17 +12602,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>270444</t>
+          <t>293561</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>270444</t>
+          <t>293561</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>270444</t>
+          <t>293561</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12649,32 +12649,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12684,32 +12684,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12719,32 +12719,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -12762,32 +12762,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12797,32 +12797,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24069</t>
+          <t>25854</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12832,32 +12832,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>26914</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34060</t>
+          <t>35448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -12875,32 +12875,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13960</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20530</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12910,32 +12910,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>47286</t>
+          <t>51457</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>43120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56739</t>
+          <t>61014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12945,32 +12945,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>61245</t>
+          <t>65729</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51514</t>
+          <t>55127</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72325</t>
+          <t>77005</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -12988,32 +12988,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>485</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13023,32 +13023,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13058,22 +13058,22 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -13101,32 +13101,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13136,32 +13136,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23472</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13171,32 +13171,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28342</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -13214,32 +13214,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13249,32 +13249,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13284,32 +13284,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -13327,32 +13327,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>61866</t>
+          <t>66365</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>57506</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>68554</t>
+          <t>74484</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13362,32 +13362,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>132621</t>
+          <t>145855</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>121565</t>
+          <t>132713</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>143129</t>
+          <t>157439</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13397,32 +13397,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>194488</t>
+          <t>212221</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>180131</t>
+          <t>197249</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>206698</t>
+          <t>226494</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,98%</t>
         </is>
       </c>
     </row>
@@ -13440,32 +13440,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13475,17 +13475,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17087</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13510,22 +13510,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -13553,17 +13553,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>102059</t>
+          <t>108576</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>102059</t>
+          <t>108576</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102059</t>
+          <t>108576</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13588,17 +13588,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>251032</t>
+          <t>275429</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>251032</t>
+          <t>275429</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>251032</t>
+          <t>275429</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13623,17 +13623,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>353092</t>
+          <t>384005</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>353092</t>
+          <t>384005</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>353092</t>
+          <t>384005</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
